--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_pet.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_pet.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1030,7 +1031,7 @@
         <v>1.0819993019104004</v>
       </c>
       <c r="E2" s="0">
-        <v>1.1077651977539062</v>
+        <v>1.1077651977539063</v>
       </c>
       <c r="F2" s="0">
         <v>1.0731761455535889</v>
@@ -1054,10 +1055,10 @@
         <v>1.2270956039428711</v>
       </c>
       <c r="M2" s="0">
-        <v>1.1316829919815063</v>
+        <v>1.1316829919815064</v>
       </c>
       <c r="N2" s="0">
-        <v>1.0931916236877441</v>
+        <v>1.0931916236877442</v>
       </c>
       <c r="O2" s="0">
         <v>1.1080087423324585</v>
@@ -1078,7 +1079,7 @@
         <v>1.1032792329788208</v>
       </c>
       <c r="U2" s="0">
-        <v>1.0723483562469482</v>
+        <v>1.0723483562469483</v>
       </c>
       <c r="V2" s="0">
         <v>1.1253553628921509</v>
@@ -1105,7 +1106,7 @@
         <v>1.1117037534713745</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.89709389209747314</v>
+        <v>0.89709389209747315</v>
       </c>
       <c r="AE2" s="0">
         <v>1.0013808012008667</v>
@@ -1126,7 +1127,7 @@
         <v>0.92290544509887695</v>
       </c>
       <c r="AK2" s="0">
-        <v>1.1148213148117065</v>
+        <v>1.1148213148117066</v>
       </c>
       <c r="AL2" s="0">
         <v>1.0272234678268433</v>
@@ -1216,7 +1217,7 @@
         <v>1.1361740827560425</v>
       </c>
       <c r="BO2" s="0">
-        <v>1.0091004371643066</v>
+        <v>1.0091004371643067</v>
       </c>
       <c r="BP2" s="0">
         <v>1.2624679803848267</v>
@@ -1327,7 +1328,7 @@
         <v>0.96951884031295776</v>
       </c>
       <c r="CZ2" s="0">
-        <v>1.0553282499313354</v>
+        <v>1.0553282499313355</v>
       </c>
       <c r="DA2" s="0">
         <v>0.85129320621490479</v>
@@ -1683,10 +1684,10 @@
         <v>0.93616533279418945</v>
       </c>
       <c r="CU3" s="0">
-        <v>0.93810111284255981</v>
+        <v>0.93810111284255982</v>
       </c>
       <c r="CV3" s="0">
-        <v>1.036384105682373</v>
+        <v>1.0363841056823731</v>
       </c>
       <c r="CW3" s="0">
         <v>1.0816346406936646</v>
@@ -1784,7 +1785,7 @@
         <v>1.0278791189193726</v>
       </c>
       <c r="I4" s="0">
-        <v>1.1235122680664062</v>
+        <v>1.1235122680664063</v>
       </c>
       <c r="J4" s="0">
         <v>0.94314146041870117</v>
@@ -1805,7 +1806,7 @@
         <v>1.0328739881515503</v>
       </c>
       <c r="P4" s="0">
-        <v>0.95517337322235107</v>
+        <v>0.95517337322235108</v>
       </c>
       <c r="Q4" s="0">
         <v>1.1225066184997559</v>
@@ -1838,7 +1839,7 @@
         <v>1.4598249197006226</v>
       </c>
       <c r="AA4" s="0">
-        <v>1.1860190629959106</v>
+        <v>1.1860190629959107</v>
       </c>
       <c r="AB4" s="0">
         <v>1.063402533531189</v>
@@ -1880,7 +1881,7 @@
         <v>1.0391892194747925</v>
       </c>
       <c r="AO4" s="0">
-        <v>1.0442264080047607</v>
+        <v>1.0442264080047608</v>
       </c>
       <c r="AP4" s="0">
         <v>1.0131869316101074</v>
@@ -1955,7 +1956,7 @@
         <v>0.71626991033554077</v>
       </c>
       <c r="BN4" s="0">
-        <v>1.0343232154846191</v>
+        <v>1.0343232154846192</v>
       </c>
       <c r="BO4" s="0">
         <v>1.1187615394592285</v>
@@ -1997,7 +1998,7 @@
         <v>0.97831380367279053</v>
       </c>
       <c r="CB4" s="0">
-        <v>0.93570160865783691</v>
+        <v>0.93570160865783692</v>
       </c>
       <c r="CC4" s="0">
         <v>1.0847040414810181</v>
@@ -2021,7 +2022,7 @@
         <v>1.1381230354309082</v>
       </c>
       <c r="CJ4" s="0">
-        <v>0.98271095752716064</v>
+        <v>0.98271095752716065</v>
       </c>
       <c r="CK4" s="0">
         <v>0.93284755945205688</v>
@@ -2030,7 +2031,7 @@
         <v>1.2977062463760376</v>
       </c>
       <c r="CM4" s="0">
-        <v>1.1749489307403564</v>
+        <v>1.1749489307403565</v>
       </c>
       <c r="CN4" s="0">
         <v>0.91423743963241577</v>
@@ -2143,13 +2144,13 @@
         <v>0.89083081483840942</v>
       </c>
       <c r="E5" s="0">
-        <v>0.86801373958587646</v>
+        <v>0.86801373958587647</v>
       </c>
       <c r="F5" s="0">
         <v>0.81559562683105469</v>
       </c>
       <c r="G5" s="0">
-        <v>0.91150349378585815</v>
+        <v>0.91150349378585816</v>
       </c>
       <c r="H5" s="0">
         <v>0.86291211843490601</v>
@@ -2164,7 +2165,7 @@
         <v>0.85379815101623535</v>
       </c>
       <c r="L5" s="0">
-        <v>0.91316217184066772</v>
+        <v>0.91316217184066773</v>
       </c>
       <c r="M5" s="0">
         <v>0.87975811958312988</v>
@@ -2239,7 +2240,7 @@
         <v>1.1035966873168945</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.95723187923431396</v>
+        <v>0.95723187923431397</v>
       </c>
       <c r="AL5" s="0">
         <v>0.85342437028884888</v>
@@ -2485,7 +2486,7 @@
         <v>1.1074516773223877</v>
       </c>
       <c r="DO5" s="0">
-        <v>1.0293035507202148</v>
+        <v>1.0293035507202149</v>
       </c>
       <c r="DP5" s="0">
         <v>1.0871745347976685</v>
@@ -2556,7 +2557,7 @@
         <v>1.1310396194458008</v>
       </c>
       <c r="S6" s="0">
-        <v>1.1691888570785522</v>
+        <v>1.1691888570785523</v>
       </c>
       <c r="T6" s="0">
         <v>1.099595308303833</v>
@@ -2586,7 +2587,7 @@
         <v>1.0841225385665894</v>
       </c>
       <c r="AC6" s="0">
-        <v>1.0450210571289062</v>
+        <v>1.0450210571289063</v>
       </c>
       <c r="AD6" s="0">
         <v>1.0237624645233154</v>
@@ -2628,7 +2629,7 @@
         <v>1.1356786489486694</v>
       </c>
       <c r="AQ6" s="0">
-        <v>1.0691132545471191</v>
+        <v>1.0691132545471192</v>
       </c>
       <c r="AR6" s="0">
         <v>1.1415632963180542</v>
@@ -2808,7 +2809,7 @@
         <v>0.99875891208648682</v>
       </c>
       <c r="CY6" s="0">
-        <v>1.0440740585327148</v>
+        <v>1.0440740585327149</v>
       </c>
       <c r="CZ6" s="0">
         <v>1.0012712478637695</v>
@@ -3005,7 +3006,7 @@
         <v>1.0874761343002319</v>
       </c>
       <c r="AS7" s="0">
-        <v>1.0065757036209106</v>
+        <v>1.0065757036209107</v>
       </c>
       <c r="AT7" s="0">
         <v>1.0837327241897583</v>
@@ -3026,7 +3027,7 @@
         <v>0.91207700967788696</v>
       </c>
       <c r="AZ7" s="0">
-        <v>0.99470126628875732</v>
+        <v>0.99470126628875733</v>
       </c>
       <c r="BA7" s="0">
         <v>0.85761016607284546</v>
@@ -3059,7 +3060,7 @@
         <v>1.0286408662796021</v>
       </c>
       <c r="BK7" s="0">
-        <v>1.1108239889144897</v>
+        <v>1.1108239889144898</v>
       </c>
       <c r="BL7" s="0">
         <v>0.98804420232772827</v>
@@ -3089,7 +3090,7 @@
         <v>0.76987248659133911</v>
       </c>
       <c r="BU7" s="0">
-        <v>1.1541279554367065</v>
+        <v>1.1541279554367066</v>
       </c>
       <c r="BV7" s="0">
         <v>0.98224723339080811</v>
@@ -3098,7 +3099,7 @@
         <v>0.99432027339935303</v>
       </c>
       <c r="BX7" s="0">
-        <v>1.254401683807373</v>
+        <v>1.2544016838073731</v>
       </c>
       <c r="BY7" s="0">
         <v>1.0403445959091187</v>
@@ -3164,7 +3165,7 @@
         <v>1.0804380178451538</v>
       </c>
       <c r="CT7" s="0">
-        <v>1.0000609159469604</v>
+        <v>1.0000609159469605</v>
       </c>
       <c r="CU7" s="0">
         <v>1.0095949172973633</v>
@@ -3194,7 +3195,7 @@
         <v>0.92649465799331665</v>
       </c>
       <c r="DD7" s="0">
-        <v>0.99666124582290649</v>
+        <v>0.9966612458229065</v>
       </c>
       <c r="DE7" s="0">
         <v>0.97316902875900269</v>
@@ -3233,7 +3234,7 @@
         <v>0.83240783214569092</v>
       </c>
       <c r="DQ7" s="0">
-        <v>0.78383255004882812</v>
+        <v>0.78383255004882813</v>
       </c>
       <c r="DR7" s="0">
         <v>0.99923866987228394</v>
@@ -3253,7 +3254,7 @@
         <v>29</v>
       </c>
       <c r="D8" s="0">
-        <v>1.3404227495193481</v>
+        <v>1.3404227495193482</v>
       </c>
       <c r="E8" s="0">
         <v>1.3040121793746948</v>
@@ -3295,7 +3296,7 @@
         <v>1.2503693103790283</v>
       </c>
       <c r="R8" s="0">
-        <v>1.2818069458007812</v>
+        <v>1.2818069458007813</v>
       </c>
       <c r="S8" s="0">
         <v>1.3380362987518311</v>
@@ -3313,7 +3314,7 @@
         <v>1.2781188488006592</v>
       </c>
       <c r="X8" s="0">
-        <v>1.0840828418731689</v>
+        <v>1.084082841873169</v>
       </c>
       <c r="Y8" s="0">
         <v>0.84254395961761475</v>
@@ -3322,13 +3323,13 @@
         <v>1.0950741767883301</v>
       </c>
       <c r="AA8" s="0">
-        <v>1.0810620784759521</v>
+        <v>1.0810620784759522</v>
       </c>
       <c r="AB8" s="0">
         <v>1.094842791557312</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.68052822351455688</v>
+        <v>0.68052822351455689</v>
       </c>
       <c r="AD8" s="0">
         <v>1.1648674011230469</v>
@@ -3337,13 +3338,13 @@
         <v>1.2258268594741821</v>
       </c>
       <c r="AF8" s="0">
-        <v>1.1272802352905273</v>
+        <v>1.1272802352905274</v>
       </c>
       <c r="AG8" s="0">
         <v>0.98974800109863281</v>
       </c>
       <c r="AH8" s="0">
-        <v>1.1220312118530273</v>
+        <v>1.1220312118530274</v>
       </c>
       <c r="AI8" s="0">
         <v>1.3539763689041138</v>
@@ -3367,7 +3368,7 @@
         <v>1.1878014802932739</v>
       </c>
       <c r="AP8" s="0">
-        <v>0.83775711059570312</v>
+        <v>0.83775711059570313</v>
       </c>
       <c r="AQ8" s="0">
         <v>1.1700620651245117</v>
@@ -3385,7 +3386,7 @@
         <v>1.2326662540435791</v>
       </c>
       <c r="AV8" s="0">
-        <v>1.1388618946075439</v>
+        <v>1.138861894607544</v>
       </c>
       <c r="AW8" s="0">
         <v>1.2070610523223877</v>
@@ -3469,7 +3470,7 @@
         <v>1.3035098314285278</v>
       </c>
       <c r="BX8" s="0">
-        <v>1.0422359704971313</v>
+        <v>1.0422359704971314</v>
       </c>
       <c r="BY8" s="0">
         <v>1.0472366809844971</v>
@@ -3535,7 +3536,7 @@
         <v>0.93189889192581177</v>
       </c>
       <c r="CT8" s="0">
-        <v>1.0083159208297729</v>
+        <v>1.008315920829773</v>
       </c>
       <c r="CU8" s="0">
         <v>1.1389232873916626</v>
@@ -3580,7 +3581,7 @@
         <v>1.0186312198638916</v>
       </c>
       <c r="DI8" s="0">
-        <v>0.94605779647827148</v>
+        <v>0.94605779647827149</v>
       </c>
       <c r="DJ8" s="0">
         <v>0.95385921001434326</v>
@@ -3651,7 +3652,7 @@
         <v>0.76071411371231079</v>
       </c>
       <c r="M9" s="0">
-        <v>0.68272924423217773</v>
+        <v>0.68272924423217774</v>
       </c>
       <c r="N9" s="0">
         <v>0.72541308403015137</v>
@@ -3711,7 +3712,7 @@
         <v>1.0745164155960083</v>
       </c>
       <c r="AG9" s="0">
-        <v>1.0238786935806274</v>
+        <v>1.0238786935806275</v>
       </c>
       <c r="AH9" s="0">
         <v>0.95264148712158203</v>
@@ -3855,7 +3856,7 @@
         <v>0.88603979349136353</v>
       </c>
       <c r="CC9" s="0">
-        <v>0.91136616468429565</v>
+        <v>0.91136616468429566</v>
       </c>
       <c r="CD9" s="0">
         <v>0.84159970283508301</v>
@@ -3933,7 +3934,7 @@
         <v>0.97089087963104248</v>
       </c>
       <c r="DC9" s="0">
-        <v>1.1516644954681396</v>
+        <v>1.1516644954681397</v>
       </c>
       <c r="DD9" s="0">
         <v>1.0276752710342407</v>
@@ -3942,7 +3943,7 @@
         <v>0.91732919216156006</v>
       </c>
       <c r="DF9" s="0">
-        <v>0.99930113554000854</v>
+        <v>0.99930113554000855</v>
       </c>
       <c r="DG9" s="0">
         <v>1.0585062503814697</v>
@@ -4049,7 +4050,7 @@
         <v>1.3313630819320679</v>
       </c>
       <c r="V10" s="0">
-        <v>1.3062893152236938</v>
+        <v>1.3062893152236939</v>
       </c>
       <c r="W10" s="0">
         <v>1.4311109781265259</v>
@@ -4073,7 +4074,7 @@
         <v>1.225556492805481</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.90952903032302856</v>
+        <v>0.90952903032302857</v>
       </c>
       <c r="AE10" s="0">
         <v>1.0456980466842651</v>
@@ -4208,7 +4209,7 @@
         <v>0.76710766553878784</v>
       </c>
       <c r="BW10" s="0">
-        <v>0.77931427955627441</v>
+        <v>0.77931427955627442</v>
       </c>
       <c r="BX10" s="0">
         <v>0.98266798257827759</v>
@@ -4262,13 +4263,13 @@
         <v>1.1120095252990723</v>
       </c>
       <c r="CO10" s="0">
-        <v>0.93126982450485229</v>
+        <v>0.9312698245048523</v>
       </c>
       <c r="CP10" s="0">
         <v>1.0909775495529175</v>
       </c>
       <c r="CQ10" s="0">
-        <v>1.0117261409759521</v>
+        <v>1.0117261409759522</v>
       </c>
       <c r="CR10" s="0">
         <v>0.92424023151397705</v>
@@ -4346,7 +4347,7 @@
         <v>0.9892268180847168</v>
       </c>
       <c r="DQ10" s="0">
-        <v>0.95344007015228271</v>
+        <v>0.95344007015228272</v>
       </c>
       <c r="DR10" s="0">
         <v>0.99622654914855957</v>
@@ -4378,7 +4379,7 @@
         <v>1.4218916893005371</v>
       </c>
       <c r="H11" s="0">
-        <v>1.4464410543441772</v>
+        <v>1.4464410543441773</v>
       </c>
       <c r="I11" s="0">
         <v>1.4787570238113403</v>
@@ -4396,7 +4397,7 @@
         <v>1.3976250886917114</v>
       </c>
       <c r="N11" s="0">
-        <v>1.4599913358688354</v>
+        <v>1.4599913358688355</v>
       </c>
       <c r="O11" s="0">
         <v>1.5291543006896973</v>
@@ -4450,7 +4451,7 @@
         <v>0.99852544069290161</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.74851143360137939</v>
+        <v>0.7485114336013794</v>
       </c>
       <c r="AG11" s="0">
         <v>1.0471067428588867</v>
@@ -4459,7 +4460,7 @@
         <v>1.3192986249923706</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.90907889604568481</v>
+        <v>0.90907889604568482</v>
       </c>
       <c r="AJ11" s="0">
         <v>0.66995155811309814</v>
@@ -4504,7 +4505,7 @@
         <v>0.90058553218841553</v>
       </c>
       <c r="AX11" s="0">
-        <v>1.3320231437683105</v>
+        <v>1.3320231437683106</v>
       </c>
       <c r="AY11" s="0">
         <v>0.85680699348449707</v>
@@ -4543,13 +4544,13 @@
         <v>1.0734671354293823</v>
       </c>
       <c r="BK11" s="0">
-        <v>0.70877456665039062</v>
+        <v>0.70877456665039063</v>
       </c>
       <c r="BL11" s="0">
         <v>0.68568837642669678</v>
       </c>
       <c r="BM11" s="0">
-        <v>1.0469584465026855</v>
+        <v>1.0469584465026856</v>
       </c>
       <c r="BN11" s="0">
         <v>1.1034359931945801</v>
